--- a/imports/company_phones.xlsx
+++ b/imports/company_phones.xlsx
@@ -5,22 +5,25 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alyona.Sachyova\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alyona.Sachyova\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{293936DD-BBCA-47E7-B102-EBD6D2ACAFFC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4EBF5AAB-B55A-48BD-9A92-D45F3BA86570}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16170" windowHeight="7890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="company_phones" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0" refMode="R1C1" calcOnSave="0"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">#REF!</definedName>
+  </definedNames>
+  <calcPr calcId="191029" refMode="R1C1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="106">
   <si>
     <t>BIN</t>
   </si>
@@ -28,98 +31,323 @@
     <t>MOBILE</t>
   </si>
   <si>
-    <t>260240021923</t>
-  </si>
-  <si>
-    <t>+7(776)557-7777,+7(776)557-7777</t>
-  </si>
-  <si>
-    <t>+7(702)972-7777</t>
-  </si>
-  <si>
-    <t>080740003407</t>
-  </si>
-  <si>
-    <t>+7(707)700-7055,+7(707)700-7055</t>
-  </si>
-  <si>
-    <t>250740900141</t>
-  </si>
-  <si>
-    <t>251240900831</t>
-  </si>
-  <si>
-    <t>070440017164</t>
-  </si>
-  <si>
-    <t>260540005932</t>
-  </si>
-  <si>
-    <t>140240005273</t>
-  </si>
-  <si>
-    <t>130840017257</t>
-  </si>
-  <si>
-    <t>060340016176</t>
-  </si>
-  <si>
-    <t>240740021630</t>
-  </si>
-  <si>
-    <t>180440025936</t>
-  </si>
-  <si>
-    <t>230440007404</t>
-  </si>
-  <si>
-    <t>200940018779</t>
-  </si>
-  <si>
-    <t>240740023419</t>
-  </si>
-  <si>
-    <t>251140900330</t>
-  </si>
-  <si>
-    <t>+7(705)256-2287,+7(705)256-2287</t>
-  </si>
-  <si>
-    <t>+7(707)950-7501,+7(707)345-4209</t>
-  </si>
-  <si>
-    <t>+7(702)750-5037,+7(702)750-5037,+7(747)882-8801</t>
-  </si>
-  <si>
-    <t>+7(701)726-2825</t>
-  </si>
-  <si>
-    <t>+7(701)742-7624,+7(701)742-7624,+7(705)765-7372</t>
-  </si>
-  <si>
-    <t>+7(775)000-0945</t>
-  </si>
-  <si>
-    <t>87719777777,+7(701)547-2828,+7(701)547-2828,+7(771)977-7777</t>
-  </si>
-  <si>
-    <t>87757949451,+7(775)794-9451</t>
-  </si>
-  <si>
-    <t>+7(702)987-9566</t>
-  </si>
-  <si>
-    <t>+7(701)100-7907</t>
-  </si>
-  <si>
-    <t>+7(707)878-7023</t>
+    <t>+7(777)087-7747,+7(777)087-7747,+7(777)811-3121</t>
+  </si>
+  <si>
+    <t>+7(702)245-9902</t>
+  </si>
+  <si>
+    <t>+7(702)400-1650,+7(702)400-1650</t>
+  </si>
+  <si>
+    <t>+7(701)588-0804</t>
+  </si>
+  <si>
+    <t>+7(701)997-0701,+7(701)997-0701</t>
+  </si>
+  <si>
+    <t>+7(777)732-4425,+7(777)732-4425</t>
+  </si>
+  <si>
+    <t>+7(778)673-4756</t>
+  </si>
+  <si>
+    <t>+7(778)382-9126</t>
+  </si>
+  <si>
+    <t>+7(707)539-4759,+7(707)539-4759</t>
+  </si>
+  <si>
+    <t>+7(701)765-4401,+7(701)765-4401</t>
+  </si>
+  <si>
+    <t>+7(702)888-8712</t>
+  </si>
+  <si>
+    <t>87772360584,+7(777)236-0584,+7(777)236-0584</t>
+  </si>
+  <si>
+    <t>+7(777)922-9447,+7(777)922-9447</t>
+  </si>
+  <si>
+    <t>+7(701)255-2778</t>
+  </si>
+  <si>
+    <t>+7(701)033-1000,+7(701)033-1000,+7(778)728-2807</t>
+  </si>
+  <si>
+    <t>+7(777)751-6555,+7(775)598-1539</t>
+  </si>
+  <si>
+    <t>+7(707)839-9061,+7(707)839-9061</t>
+  </si>
+  <si>
+    <t>+7(702)309-9666,+7(702)309-9666</t>
+  </si>
+  <si>
+    <t>+7(707)771-1162</t>
+  </si>
+  <si>
+    <t>+7(705)767-7777</t>
+  </si>
+  <si>
+    <t>+7(705)463-9999,+7(705)463-9999</t>
+  </si>
+  <si>
+    <t>+7(701)233-6474,+7(701)233-6474</t>
+  </si>
+  <si>
+    <t>+7(777)883-3177</t>
+  </si>
+  <si>
+    <t>+7(775)633-4836,+7(775)633-4836,+7(702)000-0181,+7(775)503-4562,+7(777)013-7749</t>
+  </si>
+  <si>
+    <t>+7(777)597-2288,+7(777)597-2288</t>
+  </si>
+  <si>
+    <t>87016556199,+7(701)655-6199,+7(701)655-6199</t>
+  </si>
+  <si>
+    <t>+7(705)162-0681,+7(705)162-0681</t>
+  </si>
+  <si>
+    <t>87017219516,+7(701)255-0650,+7(701)255-0650</t>
+  </si>
+  <si>
+    <t>+7(701)518-5609,+7(701)518-5609</t>
+  </si>
+  <si>
+    <t>+7(705)666-6554</t>
+  </si>
+  <si>
+    <t>+7(701)539-5995,+7(701)539-5995</t>
+  </si>
+  <si>
+    <t>+7(701)319-0213,+7(701)319-0213</t>
+  </si>
+  <si>
+    <t>+7(701)722-3174</t>
+  </si>
+  <si>
+    <t>+7(707)658-5377,+7(707)658-5777,+7(707)658-5777</t>
+  </si>
+  <si>
+    <t>87012232220,+7(701)223-2220,+7(701)223-2220</t>
+  </si>
+  <si>
+    <t>+7(777)785-2222</t>
+  </si>
+  <si>
+    <t>+7(701)761-8850,+7(701)761-8850</t>
+  </si>
+  <si>
+    <t>+7(701)350-0612,+7(747)230-2363,+7(747)230-2363</t>
+  </si>
+  <si>
+    <t>+7(701)715-6036,+7(701)715-6036</t>
+  </si>
+  <si>
+    <t>+7(775)159-1947,+7(775)159-1947,+7(702)472-8678</t>
+  </si>
+  <si>
+    <t>+7(701)212-0077,+7(701)212-0077</t>
+  </si>
+  <si>
+    <t>+7(771)586-4621</t>
+  </si>
+  <si>
+    <t>+7(705)168-9997</t>
+  </si>
+  <si>
+    <t>+7(777)417-0000</t>
+  </si>
+  <si>
+    <t>+7(778)288-6666</t>
+  </si>
+  <si>
+    <t>+7(701)316-1959</t>
+  </si>
+  <si>
+    <t>+7(777)610-5484,+7(777)610-5484</t>
+  </si>
+  <si>
+    <t>87477751103,+7(747)775-1103,+7(747)775-1103</t>
+  </si>
+  <si>
+    <t>+7(701)982-1666</t>
+  </si>
+  <si>
+    <t>191040011321</t>
+  </si>
+  <si>
+    <t>170540001762</t>
+  </si>
+  <si>
+    <t>251140901130</t>
+  </si>
+  <si>
+    <t>230840040163</t>
+  </si>
+  <si>
+    <t>241140009276</t>
+  </si>
+  <si>
+    <t>230640003062</t>
+  </si>
+  <si>
+    <t>260540007374</t>
+  </si>
+  <si>
+    <t>201140025052</t>
+  </si>
+  <si>
+    <t>250640030142</t>
+  </si>
+  <si>
+    <t>70740005305</t>
+  </si>
+  <si>
+    <t>260240901094</t>
+  </si>
+  <si>
+    <t>160540003608</t>
+  </si>
+  <si>
+    <t>180340006595</t>
+  </si>
+  <si>
+    <t>210940014392</t>
+  </si>
+  <si>
+    <t>150640025393</t>
+  </si>
+  <si>
+    <t>191140014726</t>
+  </si>
+  <si>
+    <t>210140006550</t>
+  </si>
+  <si>
+    <t>140540020466</t>
+  </si>
+  <si>
+    <t>170440013118</t>
+  </si>
+  <si>
+    <t>150840013416</t>
+  </si>
+  <si>
+    <t>160540018081</t>
+  </si>
+  <si>
+    <t>10540005723</t>
+  </si>
+  <si>
+    <t>260240008558</t>
+  </si>
+  <si>
+    <t>250940025058</t>
+  </si>
+  <si>
+    <t>230540029578</t>
+  </si>
+  <si>
+    <t>241040007910</t>
+  </si>
+  <si>
+    <t>210940043128</t>
+  </si>
+  <si>
+    <t>241240033768</t>
+  </si>
+  <si>
+    <t>201040033258</t>
+  </si>
+  <si>
+    <t>250640000943</t>
+  </si>
+  <si>
+    <t>210840026898</t>
+  </si>
+  <si>
+    <t>930940000818</t>
+  </si>
+  <si>
+    <t>20340003147</t>
+  </si>
+  <si>
+    <t>250540900322</t>
+  </si>
+  <si>
+    <t>190240014618</t>
+  </si>
+  <si>
+    <t>230940031465</t>
+  </si>
+  <si>
+    <t>120540007504</t>
+  </si>
+  <si>
+    <t>161140010807</t>
+  </si>
+  <si>
+    <t>260540017430</t>
+  </si>
+  <si>
+    <t>260440000571</t>
+  </si>
+  <si>
+    <t>260340006140</t>
+  </si>
+  <si>
+    <t>980940002972</t>
+  </si>
+  <si>
+    <t>231140018194</t>
+  </si>
+  <si>
+    <t>251240028347</t>
+  </si>
+  <si>
+    <t>210440014106</t>
+  </si>
+  <si>
+    <t>230840029757</t>
+  </si>
+  <si>
+    <t>80240017352</t>
+  </si>
+  <si>
+    <t>180940001560</t>
+  </si>
+  <si>
+    <t>240940026926</t>
+  </si>
+  <si>
+    <t>260240028603</t>
+  </si>
+  <si>
+    <t>260440011206</t>
+  </si>
+  <si>
+    <t>260440013612</t>
+  </si>
+  <si>
+    <t>260440013987</t>
+  </si>
+  <si>
+    <t>991140006990</t>
+  </si>
+  <si>
+    <t>260540008322</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -141,6 +369,10 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -155,7 +387,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -170,42 +402,25 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="3"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 2" xfId="2" xr:uid="{04BE98A3-4CD5-4E28-A3EA-DFBFE581276C}"/>
+    <cellStyle name="Обычный 3" xfId="3" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
@@ -380,11 +595,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B56"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="42" customWidth="1"/>
+    <col min="1" max="1" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="74.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="15">
@@ -395,181 +610,445 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:2" ht="15">
+      <c r="A2" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15">
+      <c r="A3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="15">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15">
+      <c r="A5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="15">
+      <c r="A6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="15">
+      <c r="A7" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="4" t="s">
+    </row>
+    <row r="8" spans="1:2" ht="15">
+      <c r="A8" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="15">
+      <c r="A9" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="15">
+      <c r="A10" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="15">
+      <c r="A11" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="15">
+      <c r="A12" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="15">
+      <c r="A13" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="15">
+      <c r="A14" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="15">
+      <c r="A15" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="15">
+      <c r="A16" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="15">
+      <c r="A17" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="15">
+      <c r="A18" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="15">
+      <c r="A19" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B19" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="15">
+      <c r="A20" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B20" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="4" t="s">
+    <row r="21" spans="1:2" ht="15">
+      <c r="A21" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B21" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="4" t="s">
+    <row r="22" spans="1:2" ht="15">
+      <c r="A22" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B22" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="4" t="s">
+    <row r="23" spans="1:2" ht="15">
+      <c r="A23" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B23" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="4" t="s">
+    <row r="24" spans="1:2" ht="15">
+      <c r="A24" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B24" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="4" t="s">
+    <row r="25" spans="1:2" ht="15">
+      <c r="A25" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B25" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="4" t="s">
+    <row r="26" spans="1:2" ht="15">
+      <c r="A26" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B26" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
-      <c r="A12" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="4" t="s">
+    <row r="27" spans="1:2" ht="15">
+      <c r="A27" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B27" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="4" t="s">
+    <row r="28" spans="1:2" ht="15">
+      <c r="A28" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B28" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" s="4" t="s">
+    <row r="29" spans="1:2" ht="15">
+      <c r="A29" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B29" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="15">
+      <c r="A30" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B30" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
-      <c r="A15" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" s="4" t="s">
+    <row r="31" spans="1:2" ht="15">
+      <c r="A31" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B31" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27" s="2"/>
-      <c r="B27" s="2"/>
-    </row>
-    <row r="28" spans="1:2">
-      <c r="A28" s="2"/>
-      <c r="B28" s="2"/>
-    </row>
-    <row r="29" spans="1:2">
-      <c r="A29" s="2"/>
-      <c r="B29" s="2"/>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2"/>
+    <row r="32" spans="1:2" ht="15">
+      <c r="A32" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B32" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="15">
+      <c r="A33" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B33" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="15">
+      <c r="A34" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B34" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="15">
+      <c r="A35" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B35" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="15">
+      <c r="A36" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B36" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="15">
+      <c r="A37" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B37" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="15">
+      <c r="A38" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B38" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="15">
+      <c r="A39" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B39" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="15">
+      <c r="A40" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B40" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="15">
+      <c r="A41" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B41" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="15">
+      <c r="A42" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B42" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="15">
+      <c r="A43" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B43" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="15">
+      <c r="A44" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B44" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="15">
+      <c r="A45" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B45" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" ht="15">
+      <c r="A46" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B46" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="15">
+      <c r="A47" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B47" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="15">
+      <c r="A48" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B48" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="15">
+      <c r="A49" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B49" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="15">
+      <c r="A50" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B50" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" ht="15">
+      <c r="A51" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B51" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" ht="15">
+      <c r="A52" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B52" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" ht="15">
+      <c r="A53" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B53" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" ht="15">
+      <c r="A54" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B54" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" ht="15">
+      <c r="A55" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B55" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" ht="15">
+      <c r="A56" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B56" t="s">
+        <v>50</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:A30">

--- a/imports/company_phones.xlsx
+++ b/imports/company_phones.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alyona.Sachyova\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alyona.Sachyova\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4EBF5AAB-B55A-48BD-9A92-D45F3BA86570}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{378744AC-F24A-486E-9533-061514494996}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16170" windowHeight="7890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="10005" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="company_phones" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191029" refMode="R1C1"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -31,84 +31,6 @@
     <t>MOBILE</t>
   </si>
   <si>
-    <t>+7(777)087-7747,+7(777)087-7747,+7(777)811-3121</t>
-  </si>
-  <si>
-    <t>+7(702)245-9902</t>
-  </si>
-  <si>
-    <t>+7(702)400-1650,+7(702)400-1650</t>
-  </si>
-  <si>
-    <t>+7(701)588-0804</t>
-  </si>
-  <si>
-    <t>+7(701)997-0701,+7(701)997-0701</t>
-  </si>
-  <si>
-    <t>+7(777)732-4425,+7(777)732-4425</t>
-  </si>
-  <si>
-    <t>+7(778)673-4756</t>
-  </si>
-  <si>
-    <t>+7(778)382-9126</t>
-  </si>
-  <si>
-    <t>+7(707)539-4759,+7(707)539-4759</t>
-  </si>
-  <si>
-    <t>+7(701)765-4401,+7(701)765-4401</t>
-  </si>
-  <si>
-    <t>+7(702)888-8712</t>
-  </si>
-  <si>
-    <t>87772360584,+7(777)236-0584,+7(777)236-0584</t>
-  </si>
-  <si>
-    <t>+7(777)922-9447,+7(777)922-9447</t>
-  </si>
-  <si>
-    <t>+7(701)255-2778</t>
-  </si>
-  <si>
-    <t>+7(701)033-1000,+7(701)033-1000,+7(778)728-2807</t>
-  </si>
-  <si>
-    <t>+7(777)751-6555,+7(775)598-1539</t>
-  </si>
-  <si>
-    <t>+7(707)839-9061,+7(707)839-9061</t>
-  </si>
-  <si>
-    <t>+7(702)309-9666,+7(702)309-9666</t>
-  </si>
-  <si>
-    <t>+7(707)771-1162</t>
-  </si>
-  <si>
-    <t>+7(705)767-7777</t>
-  </si>
-  <si>
-    <t>+7(705)463-9999,+7(705)463-9999</t>
-  </si>
-  <si>
-    <t>+7(701)233-6474,+7(701)233-6474</t>
-  </si>
-  <si>
-    <t>+7(777)883-3177</t>
-  </si>
-  <si>
-    <t>+7(775)633-4836,+7(775)633-4836,+7(702)000-0181,+7(775)503-4562,+7(777)013-7749</t>
-  </si>
-  <si>
-    <t>+7(777)597-2288,+7(777)597-2288</t>
-  </si>
-  <si>
-    <t>87016556199,+7(701)655-6199,+7(701)655-6199</t>
-  </si>
-  <si>
     <t>+7(705)162-0681,+7(705)162-0681</t>
   </si>
   <si>
@@ -178,84 +100,6 @@
     <t>+7(701)982-1666</t>
   </si>
   <si>
-    <t>191040011321</t>
-  </si>
-  <si>
-    <t>170540001762</t>
-  </si>
-  <si>
-    <t>251140901130</t>
-  </si>
-  <si>
-    <t>230840040163</t>
-  </si>
-  <si>
-    <t>241140009276</t>
-  </si>
-  <si>
-    <t>230640003062</t>
-  </si>
-  <si>
-    <t>260540007374</t>
-  </si>
-  <si>
-    <t>201140025052</t>
-  </si>
-  <si>
-    <t>250640030142</t>
-  </si>
-  <si>
-    <t>70740005305</t>
-  </si>
-  <si>
-    <t>260240901094</t>
-  </si>
-  <si>
-    <t>160540003608</t>
-  </si>
-  <si>
-    <t>180340006595</t>
-  </si>
-  <si>
-    <t>210940014392</t>
-  </si>
-  <si>
-    <t>150640025393</t>
-  </si>
-  <si>
-    <t>191140014726</t>
-  </si>
-  <si>
-    <t>210140006550</t>
-  </si>
-  <si>
-    <t>140540020466</t>
-  </si>
-  <si>
-    <t>170440013118</t>
-  </si>
-  <si>
-    <t>150840013416</t>
-  </si>
-  <si>
-    <t>160540018081</t>
-  </si>
-  <si>
-    <t>10540005723</t>
-  </si>
-  <si>
-    <t>260240008558</t>
-  </si>
-  <si>
-    <t>250940025058</t>
-  </si>
-  <si>
-    <t>230540029578</t>
-  </si>
-  <si>
-    <t>241040007910</t>
-  </si>
-  <si>
     <t>210940043128</t>
   </si>
   <si>
@@ -341,6 +185,162 @@
   </si>
   <si>
     <t>260540008322</t>
+  </si>
+  <si>
+    <t>+7(707)524-5249,+7(707)524-5249,+7(700)080-8038</t>
+  </si>
+  <si>
+    <t>87776999558,+7(777)699-9558,+7(777)699-9558</t>
+  </si>
+  <si>
+    <t>+7(701)280-1859,+7(701)280-1859</t>
+  </si>
+  <si>
+    <t>+7(707)653-3016,+7(702)137-1316,+7(702)137-1316</t>
+  </si>
+  <si>
+    <t>+7(771)537-8291</t>
+  </si>
+  <si>
+    <t>+7(701)991-9977,+7(701)991-9977</t>
+  </si>
+  <si>
+    <t>+7(701)711-5642,+7(701)711-5642</t>
+  </si>
+  <si>
+    <t>+7(705)576-7706,+7(705)576-7706,+7(707)633-7529</t>
+  </si>
+  <si>
+    <t>87017471987,+7(701)747-1987,+7(701)747-1987</t>
+  </si>
+  <si>
+    <t>+7(701)319-4110,+7(701)319-4110</t>
+  </si>
+  <si>
+    <t>+7(701)222-1829</t>
+  </si>
+  <si>
+    <t>+7(701)551-5533,+7(701)551-5533</t>
+  </si>
+  <si>
+    <t>+7(777)774-0010</t>
+  </si>
+  <si>
+    <t>+7(707)315-7890</t>
+  </si>
+  <si>
+    <t>+7(701)895-5577,+7(701)895-5577</t>
+  </si>
+  <si>
+    <t>+7(701)888-8955,+7(701)888-8955</t>
+  </si>
+  <si>
+    <t>+7(777)602-4833,+7(777)602-4833,+7(777)749-2018</t>
+  </si>
+  <si>
+    <t>+7(708)546-3859</t>
+  </si>
+  <si>
+    <t>+7(776)197-7634,+7(707)357-9397,+7(776)209-5076</t>
+  </si>
+  <si>
+    <t>+7(702)931-7777,+7(702)931-7777</t>
+  </si>
+  <si>
+    <t>+7(701)000-0392,+7(701)000-0392</t>
+  </si>
+  <si>
+    <t>+7(701)714-7852,+7(701)714-7852</t>
+  </si>
+  <si>
+    <t>+7(777)658-2292,+7(777)658-2292</t>
+  </si>
+  <si>
+    <t>+7(701)566-0400,+7(701)566-0400</t>
+  </si>
+  <si>
+    <t>+7(701)522-4031,+7(701)522-4031</t>
+  </si>
+  <si>
+    <t>+7(701)565-1514,+7(701)565-1514</t>
+  </si>
+  <si>
+    <t>110140007716</t>
+  </si>
+  <si>
+    <t>120440013515</t>
+  </si>
+  <si>
+    <t>150640016730</t>
+  </si>
+  <si>
+    <t>170840003155</t>
+  </si>
+  <si>
+    <t>170940017087</t>
+  </si>
+  <si>
+    <t>191040011867</t>
+  </si>
+  <si>
+    <t>200440008165</t>
+  </si>
+  <si>
+    <t>200740017020</t>
+  </si>
+  <si>
+    <t>220940037214</t>
+  </si>
+  <si>
+    <t>231040024610</t>
+  </si>
+  <si>
+    <t>231140021174</t>
+  </si>
+  <si>
+    <t>240740021501</t>
+  </si>
+  <si>
+    <t>240940019963</t>
+  </si>
+  <si>
+    <t>250440900369</t>
+  </si>
+  <si>
+    <t>251140901031</t>
+  </si>
+  <si>
+    <t>260140012851</t>
+  </si>
+  <si>
+    <t>260140900342</t>
+  </si>
+  <si>
+    <t>260240019674</t>
+  </si>
+  <si>
+    <t>260240032017</t>
+  </si>
+  <si>
+    <t>260340012254</t>
+  </si>
+  <si>
+    <t>260440008676</t>
+  </si>
+  <si>
+    <t>30740000189</t>
+  </si>
+  <si>
+    <t>31140005468</t>
+  </si>
+  <si>
+    <t>60740008536</t>
+  </si>
+  <si>
+    <t>70540013557</t>
+  </si>
+  <si>
+    <t>81140001088</t>
   </si>
 </sst>
 </file>
@@ -612,442 +612,442 @@
     </row>
     <row r="2" spans="1:2" ht="15">
       <c r="A2" s="2" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15">
       <c r="A3" s="2" t="s">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15">
       <c r="A4" s="2" t="s">
-        <v>53</v>
+        <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15">
       <c r="A5" s="2" t="s">
-        <v>54</v>
+        <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15">
       <c r="A6" s="2" t="s">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15">
       <c r="A7" s="2" t="s">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="15">
       <c r="A8" s="2" t="s">
-        <v>57</v>
+        <v>86</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="15">
       <c r="A9" s="2" t="s">
-        <v>58</v>
+        <v>87</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="15">
       <c r="A10" s="2" t="s">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="15">
       <c r="A11" s="2" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="15">
       <c r="A12" s="2" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="15">
       <c r="A13" s="2" t="s">
-        <v>62</v>
+        <v>91</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="15">
       <c r="A14" s="2" t="s">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="15">
       <c r="A15" s="2" t="s">
-        <v>64</v>
+        <v>93</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="15">
       <c r="A16" s="2" t="s">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="15">
       <c r="A17" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B17" t="s">
         <v>66</v>
-      </c>
-      <c r="B17" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="15">
       <c r="A18" s="2" t="s">
-        <v>67</v>
+        <v>96</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="15">
       <c r="A19" s="2" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="15">
       <c r="A20" s="2" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="15">
       <c r="A21" s="2" t="s">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>78</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="15">
       <c r="A22" s="2" t="s">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="15">
       <c r="A23" s="2" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="15">
       <c r="A24" s="2" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>76</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="15">
       <c r="A25" s="2" t="s">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>77</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="15">
       <c r="A26" s="2" t="s">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="15">
       <c r="A27" s="2" t="s">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="15">
       <c r="A28" s="2" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="15">
       <c r="A29" s="2" t="s">
-        <v>78</v>
+        <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>28</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="15">
       <c r="A30" s="2" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>29</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="15">
       <c r="A31" s="2" t="s">
-        <v>80</v>
+        <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>30</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="15">
       <c r="A32" s="2" t="s">
-        <v>81</v>
+        <v>29</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="15">
       <c r="A33" s="2" t="s">
-        <v>82</v>
+        <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="15">
       <c r="A34" s="2" t="s">
-        <v>83</v>
+        <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="15">
       <c r="A35" s="2" t="s">
-        <v>84</v>
+        <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="15">
       <c r="A36" s="2" t="s">
-        <v>85</v>
+        <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="15">
       <c r="A37" s="2" t="s">
-        <v>86</v>
+        <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="15">
       <c r="A38" s="2" t="s">
-        <v>87</v>
+        <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="15">
       <c r="A39" s="2" t="s">
-        <v>88</v>
+        <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="15">
       <c r="A40" s="2" t="s">
-        <v>89</v>
+        <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="15">
       <c r="A41" s="2" t="s">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="15">
       <c r="A42" s="2" t="s">
-        <v>91</v>
+        <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="15">
       <c r="A43" s="2" t="s">
-        <v>92</v>
+        <v>40</v>
       </c>
       <c r="B43" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="15">
       <c r="A44" s="2" t="s">
-        <v>93</v>
+        <v>41</v>
       </c>
       <c r="B44" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="15">
       <c r="A45" s="2" t="s">
-        <v>94</v>
+        <v>42</v>
       </c>
       <c r="B45" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="15">
       <c r="A46" s="2" t="s">
-        <v>95</v>
+        <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="15">
       <c r="A47" s="2" t="s">
-        <v>96</v>
+        <v>44</v>
       </c>
       <c r="B47" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="15">
       <c r="A48" s="2" t="s">
-        <v>97</v>
+        <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="15">
       <c r="A49" s="2" t="s">
-        <v>98</v>
+        <v>46</v>
       </c>
       <c r="B49" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="15">
       <c r="A50" s="2" t="s">
-        <v>99</v>
+        <v>47</v>
       </c>
       <c r="B50" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
     </row>
     <row r="51" spans="1:2" ht="15">
       <c r="A51" s="2" t="s">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="B51" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="15">
       <c r="A52" s="2" t="s">
-        <v>101</v>
+        <v>49</v>
       </c>
       <c r="B52" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="15">
       <c r="A53" s="2" t="s">
-        <v>102</v>
+        <v>50</v>
       </c>
       <c r="B53" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
     </row>
     <row r="54" spans="1:2" ht="15">
       <c r="A54" s="2" t="s">
-        <v>103</v>
+        <v>51</v>
       </c>
       <c r="B54" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
     </row>
     <row r="55" spans="1:2" ht="15">
       <c r="A55" s="2" t="s">
-        <v>104</v>
+        <v>52</v>
       </c>
       <c r="B55" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
     </row>
     <row r="56" spans="1:2" ht="15">
       <c r="A56" s="2" t="s">
-        <v>105</v>
+        <v>53</v>
       </c>
       <c r="B56" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/imports/company_phones.xlsx
+++ b/imports/company_phones.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alyona.Sachyova\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alyona.Sachyova\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{378744AC-F24A-486E-9533-061514494996}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4EBF5AAB-B55A-48BD-9A92-D45F3BA86570}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="10005" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16170" windowHeight="7890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="company_phones" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" refMode="R1C1"/>
 </workbook>
 </file>
 
@@ -31,6 +31,84 @@
     <t>MOBILE</t>
   </si>
   <si>
+    <t>+7(777)087-7747,+7(777)087-7747,+7(777)811-3121</t>
+  </si>
+  <si>
+    <t>+7(702)245-9902</t>
+  </si>
+  <si>
+    <t>+7(702)400-1650,+7(702)400-1650</t>
+  </si>
+  <si>
+    <t>+7(701)588-0804</t>
+  </si>
+  <si>
+    <t>+7(701)997-0701,+7(701)997-0701</t>
+  </si>
+  <si>
+    <t>+7(777)732-4425,+7(777)732-4425</t>
+  </si>
+  <si>
+    <t>+7(778)673-4756</t>
+  </si>
+  <si>
+    <t>+7(778)382-9126</t>
+  </si>
+  <si>
+    <t>+7(707)539-4759,+7(707)539-4759</t>
+  </si>
+  <si>
+    <t>+7(701)765-4401,+7(701)765-4401</t>
+  </si>
+  <si>
+    <t>+7(702)888-8712</t>
+  </si>
+  <si>
+    <t>87772360584,+7(777)236-0584,+7(777)236-0584</t>
+  </si>
+  <si>
+    <t>+7(777)922-9447,+7(777)922-9447</t>
+  </si>
+  <si>
+    <t>+7(701)255-2778</t>
+  </si>
+  <si>
+    <t>+7(701)033-1000,+7(701)033-1000,+7(778)728-2807</t>
+  </si>
+  <si>
+    <t>+7(777)751-6555,+7(775)598-1539</t>
+  </si>
+  <si>
+    <t>+7(707)839-9061,+7(707)839-9061</t>
+  </si>
+  <si>
+    <t>+7(702)309-9666,+7(702)309-9666</t>
+  </si>
+  <si>
+    <t>+7(707)771-1162</t>
+  </si>
+  <si>
+    <t>+7(705)767-7777</t>
+  </si>
+  <si>
+    <t>+7(705)463-9999,+7(705)463-9999</t>
+  </si>
+  <si>
+    <t>+7(701)233-6474,+7(701)233-6474</t>
+  </si>
+  <si>
+    <t>+7(777)883-3177</t>
+  </si>
+  <si>
+    <t>+7(775)633-4836,+7(775)633-4836,+7(702)000-0181,+7(775)503-4562,+7(777)013-7749</t>
+  </si>
+  <si>
+    <t>+7(777)597-2288,+7(777)597-2288</t>
+  </si>
+  <si>
+    <t>87016556199,+7(701)655-6199,+7(701)655-6199</t>
+  </si>
+  <si>
     <t>+7(705)162-0681,+7(705)162-0681</t>
   </si>
   <si>
@@ -100,6 +178,84 @@
     <t>+7(701)982-1666</t>
   </si>
   <si>
+    <t>191040011321</t>
+  </si>
+  <si>
+    <t>170540001762</t>
+  </si>
+  <si>
+    <t>251140901130</t>
+  </si>
+  <si>
+    <t>230840040163</t>
+  </si>
+  <si>
+    <t>241140009276</t>
+  </si>
+  <si>
+    <t>230640003062</t>
+  </si>
+  <si>
+    <t>260540007374</t>
+  </si>
+  <si>
+    <t>201140025052</t>
+  </si>
+  <si>
+    <t>250640030142</t>
+  </si>
+  <si>
+    <t>70740005305</t>
+  </si>
+  <si>
+    <t>260240901094</t>
+  </si>
+  <si>
+    <t>160540003608</t>
+  </si>
+  <si>
+    <t>180340006595</t>
+  </si>
+  <si>
+    <t>210940014392</t>
+  </si>
+  <si>
+    <t>150640025393</t>
+  </si>
+  <si>
+    <t>191140014726</t>
+  </si>
+  <si>
+    <t>210140006550</t>
+  </si>
+  <si>
+    <t>140540020466</t>
+  </si>
+  <si>
+    <t>170440013118</t>
+  </si>
+  <si>
+    <t>150840013416</t>
+  </si>
+  <si>
+    <t>160540018081</t>
+  </si>
+  <si>
+    <t>10540005723</t>
+  </si>
+  <si>
+    <t>260240008558</t>
+  </si>
+  <si>
+    <t>250940025058</t>
+  </si>
+  <si>
+    <t>230540029578</t>
+  </si>
+  <si>
+    <t>241040007910</t>
+  </si>
+  <si>
     <t>210940043128</t>
   </si>
   <si>
@@ -185,162 +341,6 @@
   </si>
   <si>
     <t>260540008322</t>
-  </si>
-  <si>
-    <t>+7(707)524-5249,+7(707)524-5249,+7(700)080-8038</t>
-  </si>
-  <si>
-    <t>87776999558,+7(777)699-9558,+7(777)699-9558</t>
-  </si>
-  <si>
-    <t>+7(701)280-1859,+7(701)280-1859</t>
-  </si>
-  <si>
-    <t>+7(707)653-3016,+7(702)137-1316,+7(702)137-1316</t>
-  </si>
-  <si>
-    <t>+7(771)537-8291</t>
-  </si>
-  <si>
-    <t>+7(701)991-9977,+7(701)991-9977</t>
-  </si>
-  <si>
-    <t>+7(701)711-5642,+7(701)711-5642</t>
-  </si>
-  <si>
-    <t>+7(705)576-7706,+7(705)576-7706,+7(707)633-7529</t>
-  </si>
-  <si>
-    <t>87017471987,+7(701)747-1987,+7(701)747-1987</t>
-  </si>
-  <si>
-    <t>+7(701)319-4110,+7(701)319-4110</t>
-  </si>
-  <si>
-    <t>+7(701)222-1829</t>
-  </si>
-  <si>
-    <t>+7(701)551-5533,+7(701)551-5533</t>
-  </si>
-  <si>
-    <t>+7(777)774-0010</t>
-  </si>
-  <si>
-    <t>+7(707)315-7890</t>
-  </si>
-  <si>
-    <t>+7(701)895-5577,+7(701)895-5577</t>
-  </si>
-  <si>
-    <t>+7(701)888-8955,+7(701)888-8955</t>
-  </si>
-  <si>
-    <t>+7(777)602-4833,+7(777)602-4833,+7(777)749-2018</t>
-  </si>
-  <si>
-    <t>+7(708)546-3859</t>
-  </si>
-  <si>
-    <t>+7(776)197-7634,+7(707)357-9397,+7(776)209-5076</t>
-  </si>
-  <si>
-    <t>+7(702)931-7777,+7(702)931-7777</t>
-  </si>
-  <si>
-    <t>+7(701)000-0392,+7(701)000-0392</t>
-  </si>
-  <si>
-    <t>+7(701)714-7852,+7(701)714-7852</t>
-  </si>
-  <si>
-    <t>+7(777)658-2292,+7(777)658-2292</t>
-  </si>
-  <si>
-    <t>+7(701)566-0400,+7(701)566-0400</t>
-  </si>
-  <si>
-    <t>+7(701)522-4031,+7(701)522-4031</t>
-  </si>
-  <si>
-    <t>+7(701)565-1514,+7(701)565-1514</t>
-  </si>
-  <si>
-    <t>110140007716</t>
-  </si>
-  <si>
-    <t>120440013515</t>
-  </si>
-  <si>
-    <t>150640016730</t>
-  </si>
-  <si>
-    <t>170840003155</t>
-  </si>
-  <si>
-    <t>170940017087</t>
-  </si>
-  <si>
-    <t>191040011867</t>
-  </si>
-  <si>
-    <t>200440008165</t>
-  </si>
-  <si>
-    <t>200740017020</t>
-  </si>
-  <si>
-    <t>220940037214</t>
-  </si>
-  <si>
-    <t>231040024610</t>
-  </si>
-  <si>
-    <t>231140021174</t>
-  </si>
-  <si>
-    <t>240740021501</t>
-  </si>
-  <si>
-    <t>240940019963</t>
-  </si>
-  <si>
-    <t>250440900369</t>
-  </si>
-  <si>
-    <t>251140901031</t>
-  </si>
-  <si>
-    <t>260140012851</t>
-  </si>
-  <si>
-    <t>260140900342</t>
-  </si>
-  <si>
-    <t>260240019674</t>
-  </si>
-  <si>
-    <t>260240032017</t>
-  </si>
-  <si>
-    <t>260340012254</t>
-  </si>
-  <si>
-    <t>260440008676</t>
-  </si>
-  <si>
-    <t>30740000189</t>
-  </si>
-  <si>
-    <t>31140005468</t>
-  </si>
-  <si>
-    <t>60740008536</t>
-  </si>
-  <si>
-    <t>70540013557</t>
-  </si>
-  <si>
-    <t>81140001088</t>
   </si>
 </sst>
 </file>
@@ -612,442 +612,442 @@
     </row>
     <row r="2" spans="1:2" ht="15">
       <c r="A2" s="2" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15">
       <c r="A3" s="2" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15">
       <c r="A4" s="2" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15">
       <c r="A5" s="2" t="s">
-        <v>83</v>
+        <v>54</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15">
       <c r="A6" s="2" t="s">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15">
       <c r="A7" s="2" t="s">
-        <v>85</v>
+        <v>56</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="15">
       <c r="A8" s="2" t="s">
-        <v>86</v>
+        <v>57</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="15">
       <c r="A9" s="2" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="15">
       <c r="A10" s="2" t="s">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="15">
       <c r="A11" s="2" t="s">
-        <v>89</v>
+        <v>60</v>
       </c>
       <c r="B11" t="s">
-        <v>59</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="15">
       <c r="A12" s="2" t="s">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="15">
       <c r="A13" s="2" t="s">
-        <v>91</v>
+        <v>62</v>
       </c>
       <c r="B13" t="s">
-        <v>69</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="15">
       <c r="A14" s="2" t="s">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="B14" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="15">
       <c r="A15" s="2" t="s">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="B15" t="s">
-        <v>74</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="15">
       <c r="A16" s="2" t="s">
-        <v>94</v>
+        <v>65</v>
       </c>
       <c r="B16" t="s">
-        <v>60</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="15">
       <c r="A17" s="2" t="s">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="B17" t="s">
-        <v>66</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="15">
       <c r="A18" s="2" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="B18" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="15">
       <c r="A19" s="2" t="s">
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="B19" t="s">
-        <v>62</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="15">
       <c r="A20" s="2" t="s">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="B20" t="s">
-        <v>71</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="15">
       <c r="A21" s="2" t="s">
-        <v>99</v>
+        <v>70</v>
       </c>
       <c r="B21" t="s">
-        <v>78</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="15">
       <c r="A22" s="2" t="s">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="B22" t="s">
-        <v>75</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="15">
       <c r="A23" s="2" t="s">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="B23" t="s">
-        <v>61</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="15">
       <c r="A24" s="2" t="s">
-        <v>102</v>
+        <v>73</v>
       </c>
       <c r="B24" t="s">
-        <v>76</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="15">
       <c r="A25" s="2" t="s">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="B25" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="15">
       <c r="A26" s="2" t="s">
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="B26" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="15">
       <c r="A27" s="2" t="s">
-        <v>105</v>
+        <v>76</v>
       </c>
       <c r="B27" t="s">
-        <v>57</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="15">
       <c r="A28" s="2" t="s">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="B28" t="s">
-        <v>2</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="15">
       <c r="A29" s="2" t="s">
-        <v>26</v>
+        <v>78</v>
       </c>
       <c r="B29" t="s">
-        <v>2</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="15">
       <c r="A30" s="2" t="s">
-        <v>27</v>
+        <v>79</v>
       </c>
       <c r="B30" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="15">
       <c r="A31" s="2" t="s">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="B31" t="s">
-        <v>4</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="15">
       <c r="A32" s="2" t="s">
-        <v>29</v>
+        <v>81</v>
       </c>
       <c r="B32" t="s">
-        <v>6</v>
+        <v>32</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="15">
       <c r="A33" s="2" t="s">
-        <v>30</v>
+        <v>82</v>
       </c>
       <c r="B33" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="15">
       <c r="A34" s="2" t="s">
-        <v>31</v>
+        <v>83</v>
       </c>
       <c r="B34" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="15">
       <c r="A35" s="2" t="s">
-        <v>32</v>
+        <v>84</v>
       </c>
       <c r="B35" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="15">
       <c r="A36" s="2" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="B36" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="15">
       <c r="A37" s="2" t="s">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="B37" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="15">
       <c r="A38" s="2" t="s">
-        <v>35</v>
+        <v>87</v>
       </c>
       <c r="B38" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="15">
       <c r="A39" s="2" t="s">
-        <v>36</v>
+        <v>88</v>
       </c>
       <c r="B39" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="15">
       <c r="A40" s="2" t="s">
-        <v>37</v>
+        <v>89</v>
       </c>
       <c r="B40" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="15">
       <c r="A41" s="2" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="B41" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="15">
       <c r="A42" s="2" t="s">
-        <v>39</v>
+        <v>91</v>
       </c>
       <c r="B42" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="15">
       <c r="A43" s="2" t="s">
-        <v>40</v>
+        <v>92</v>
       </c>
       <c r="B43" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="15">
       <c r="A44" s="2" t="s">
-        <v>41</v>
+        <v>93</v>
       </c>
       <c r="B44" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="15">
       <c r="A45" s="2" t="s">
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="B45" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="15">
       <c r="A46" s="2" t="s">
-        <v>43</v>
+        <v>95</v>
       </c>
       <c r="B46" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="15">
       <c r="A47" s="2" t="s">
-        <v>44</v>
+        <v>96</v>
       </c>
       <c r="B47" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="15">
       <c r="A48" s="2" t="s">
-        <v>45</v>
+        <v>97</v>
       </c>
       <c r="B48" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="15">
       <c r="A49" s="2" t="s">
-        <v>46</v>
+        <v>98</v>
       </c>
       <c r="B49" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="15">
       <c r="A50" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B50" t="s">
         <v>47</v>
-      </c>
-      <c r="B50" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="51" spans="1:2" ht="15">
       <c r="A51" s="2" t="s">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="B51" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="15">
       <c r="A52" s="2" t="s">
-        <v>49</v>
+        <v>101</v>
       </c>
       <c r="B52" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="15">
       <c r="A53" s="2" t="s">
-        <v>50</v>
+        <v>102</v>
       </c>
       <c r="B53" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
     </row>
     <row r="54" spans="1:2" ht="15">
       <c r="A54" s="2" t="s">
-        <v>51</v>
+        <v>103</v>
       </c>
       <c r="B54" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
     </row>
     <row r="55" spans="1:2" ht="15">
       <c r="A55" s="2" t="s">
-        <v>52</v>
+        <v>104</v>
       </c>
       <c r="B55" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
     </row>
     <row r="56" spans="1:2" ht="15">
       <c r="A56" s="2" t="s">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="B56" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
